--- a/artfynd/A 25456-2023 artfynd.xlsx
+++ b/artfynd/A 25456-2023 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonathan Börjesson, Karl-Erik Gustafsson</t>
+          <t>Karl-Erik Gustafsson, Jonathan Börjesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25456-2023 artfynd.xlsx
+++ b/artfynd/A 25456-2023 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl-Erik Gustafsson, Jonathan Börjesson</t>
+          <t>Jonathan Börjesson, Karl-Erik Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25456-2023 artfynd.xlsx
+++ b/artfynd/A 25456-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126750042</v>
       </c>
       <c r="B2" t="n">
-        <v>43086</v>
+        <v>43090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonathan Börjesson, Karl-Erik Gustafsson</t>
+          <t>Karl-Erik Gustafsson, Jonathan Börjesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25456-2023 artfynd.xlsx
+++ b/artfynd/A 25456-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126750042</v>
       </c>
       <c r="B2" t="n">
-        <v>43090</v>
+        <v>43086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl-Erik Gustafsson, Jonathan Börjesson</t>
+          <t>Jonathan Börjesson, Karl-Erik Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25456-2023 artfynd.xlsx
+++ b/artfynd/A 25456-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126750042</v>
+        <v>126717374</v>
       </c>
       <c r="B2" t="n">
-        <v>43090</v>
+        <v>43326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,20 +717,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fästan, Sk</t>
+          <t>Alkärret, Maglehem, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448446</v>
+        <v>448430</v>
       </c>
       <c r="R2" t="n">
-        <v>6181478</v>
+        <v>6181491</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,15 +778,130 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Johan Rickardsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Johan Rickardsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126750042</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101732</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Krattsnabbvinge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Satyrium ilicis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Esper, 1779)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fästan, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>448446</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6181478</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jonathan Börjesson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Karl-Erik Gustafsson, Jonathan Börjesson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25456-2023 artfynd.xlsx
+++ b/artfynd/A 25456-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134992341</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126717374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,8 +1032,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126750042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25456-2023 artfynd.xlsx
+++ b/artfynd/A 25456-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134992341</v>
       </c>
       <c r="B2" t="n">
-        <v>42205</v>
+        <v>42210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
